--- a/Datasets/Public Workshop Data Records.xlsx
+++ b/Datasets/Public Workshop Data Records.xlsx
@@ -457,8 +457,7 @@
     <t>https://steamcommunity.com/sharedfiles/filedetails/?id=3577494132</t>
   </si>
   <si>
-    <t xml:space="preserve">Avian Boids: Realistic Bird Swarms
-</t>
+    <t>Avian Boids: Realistic Bird Swarms</t>
   </si>
   <si>
     <t>https://steamcommunity.com/sharedfiles/filedetails/?id=3633311766</t>
